--- a/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
+++ b/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6E9151-AACD-4B32-B295-0F5F3626D1D9}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC1E9975-3230-4E30-BC45-FCC3D56D7D5F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{953A7621-5D67-4682-9C09-2CA2A8669DE6}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="926">
   <si>
     <t>TABLA AGREGADA ALERTAS PLAFT - AWS</t>
   </si>
@@ -2816,9 +2816,6 @@
   </si>
   <si>
     <t>Cantidad de trx sin envio la exterior en los ultimos 12 meses</t>
-  </si>
-  <si>
-    <t>Falta</t>
   </si>
   <si>
     <t>Ord</t>
@@ -2828,7 +2825,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2919,6 +2916,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -2995,18 +2998,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3156,22 +3159,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3272,10 +3264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3320,6 +3308,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -3712,24 +3706,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
@@ -3737,12 +3731,12 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
@@ -3750,25 +3744,25 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="51"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="54"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
@@ -9207,17 +9201,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DCCAE6-0E9B-4753-90E8-43F48446DEA8}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" customWidth="1"/>
-    <col min="3" max="3" width="104.6328125" customWidth="1"/>
+    <col min="3" max="3" width="120.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="10" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>9</v>
@@ -9225,495 +9219,366 @@
       <c r="C1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="53" t="s">
         <v>559</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2">
-        <v>0.50809879999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="53" t="s">
         <v>112</v>
       </c>
       <c r="C3" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3">
-        <v>0.55158819999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="37" t="s">
         <v>891</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>877</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4">
-        <v>0.66200119999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="53" t="s">
         <v>445</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>446</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5">
-        <v>0.20248437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="53" t="s">
         <v>493</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6">
-        <v>0.50723076</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="53" t="s">
         <v>856</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>857</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7">
-        <v>0.22907783000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="53" t="s">
         <v>634</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>635</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8">
-        <v>0.31891456000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="57" t="s">
         <v>918</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>883</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9">
-        <v>0.103008695</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="53" t="s">
         <v>670</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>671</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10">
-        <v>0.2037564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="53" t="s">
         <v>161</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11">
-        <v>0.35607477999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="53" t="s">
         <v>460</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12">
-        <v>2.6368237999999999E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="53" t="s">
         <v>643</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>644</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13">
-        <v>2.0175342999999998E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="53" t="s">
         <v>655</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>656</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14">
-        <v>0.118840374</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="53" t="s">
         <v>457</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>458</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15">
-        <v>2.8444325999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="37" t="s">
         <v>894</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>887</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16">
-        <v>3.5924204000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="53" t="s">
         <v>888</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>920</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17">
-        <v>2.7962926999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="53" t="s">
         <v>733</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>734</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18">
-        <v>0.2653201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="37" t="s">
         <v>895</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>885</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19">
-        <v>4.7678597000000003E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="53" t="s">
         <v>269</v>
       </c>
       <c r="C20" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20">
-        <v>2.2723411999999998E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="53" t="s">
         <v>266</v>
       </c>
       <c r="C21" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21">
-        <v>1.7494446E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="53" t="s">
         <v>721</v>
       </c>
       <c r="C22" s="28" t="s">
         <v>722</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22">
-        <v>7.9125040000000008E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="54" t="s">
         <v>889</v>
       </c>
       <c r="C23" s="28" t="s">
         <v>922</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23">
-        <v>2.9770036E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="53" t="s">
         <v>173</v>
       </c>
       <c r="C24" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24">
-        <v>3.1605243999999998E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="53" t="s">
         <v>896</v>
       </c>
       <c r="C25" t="s">
         <v>924</v>
       </c>
-      <c r="D25" s="28"/>
-      <c r="E25">
-        <v>1.5604318E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="53" t="s">
         <v>149</v>
       </c>
       <c r="C26" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26">
-        <v>5.6675323E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="55" t="s">
         <v>850</v>
       </c>
       <c r="C27" s="28" t="s">
         <v>851</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27">
-        <v>3.6020955999999998E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="53" t="s">
         <v>248</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28">
-        <v>2.0265600000000002E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="53" t="s">
         <v>239</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29">
-        <v>1.3661184E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="53" t="s">
         <v>890</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>923</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30">
-        <v>4.3424240000000001E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="53" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31">
-        <v>0.65039029999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="53" t="s">
         <v>60</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32">
-        <v>0.17080948000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1">
+    </row>
+    <row r="33" spans="1:3" ht="15" thickBot="1">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="53" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33">
-        <v>0.13392287</v>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="B35" s="56" t="s">
+        <v>882</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C33">
     <sortCondition ref="A2:A33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
